--- a/RESULTS/tables/survival_cox_baseline_development_top_features.xlsx
+++ b/RESULTS/tables/survival_cox_baseline_development_top_features.xlsx
@@ -463,271 +463,289 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADL_last_score</t>
+          <t>ADL_總分_max</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADL Last Score</t>
+          <t>ADL Total Max</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3696958260587697</v>
+        <v>0.1212542658001659</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3438838239577022</v>
+        <v>0.0848203788991</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3974452832131097</v>
+        <v>0.1733380251958919</v>
       </c>
       <c r="F2" t="n">
-        <v>6.158654774544767e-160</v>
+        <v>5.706538027428568e-31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADL_總分_max</t>
+          <t>ADL_Max</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADL Total Max</t>
+          <t>ADL Maximum</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3514055871279629</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+        <v>0.3073659755962531</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2014884685331843</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4688796517339005</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.36851772580092e-08</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADL_Max</t>
+          <t>ADL_first_score</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADL Maximum</t>
+          <t>ADL First Score</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3514054692548642</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+        <v>12.33570538319222</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.486805672479194</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16.0401332708179</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.825325808784278e-78</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADL_first_score</t>
+          <t>六個月內住院次數</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADL First Score</t>
+          <t>Hospitalizations within 6 Months</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.263747582748711</v>
+        <v>1.219734899879974</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9678798771332657</v>
+        <v>1.195327562661074</v>
       </c>
       <c r="E5" t="n">
-        <v>1.650058019217723</v>
+        <v>1.244640609368306</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08541456450737529</v>
+        <v>1.148384030647452e-82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>六個月內住院次數</t>
+          <t>ADL_Min</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hospitalizations within 6 Months</t>
+          <t>ADL Minimum</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.231542683248816</v>
+        <v>0.3061709170475488</v>
       </c>
       <c r="D6" t="n">
-        <v>1.207026108226808</v>
+        <v>0.2741802200744256</v>
       </c>
       <c r="E6" t="n">
-        <v>1.256557227988888</v>
+        <v>0.3418942125740922</v>
       </c>
       <c r="F6" t="n">
-        <v>1.270862796110769e-91</v>
+        <v>4.177521190196632e-98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADL_Min</t>
+          <t>ADL_last_score</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADL Minimum</t>
+          <t>ADL Last Score</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.284216289454055</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+        <v>4.242209593166028</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.98541287795296</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4.515552787994551</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BW_last</t>
+          <t>使用呼吸輔具</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Body Weight (Last)</t>
+          <t>Use of Respiratory Aid</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9295979787091498</v>
+        <v>1.101866265483333</v>
       </c>
       <c r="D8" t="n">
-        <v>0.853413384036808</v>
+        <v>1.077528513952472</v>
       </c>
       <c r="E8" t="n">
-        <v>1.012583606238434</v>
+        <v>1.126753725111853</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09425626162068874</v>
+        <v>1.701645069109407e-17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BW_first</t>
+          <t>first_has_feeding_tube</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Body Weight (First)</t>
+          <t>Has Feeding Tube (First)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.7735176853658143</v>
+        <v>1.096497509419664</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7079907918975634</v>
+        <v>1.043177099540523</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8451093099248346</v>
+        <v>1.152543310903866</v>
       </c>
       <c r="F9" t="n">
-        <v>1.297829204136197e-08</v>
+        <v>0.0002923276497292924</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>使用呼吸輔具</t>
+          <t>last_has_feeding_tube</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Use of Respiratory Aid</t>
+          <t>Has Feeding Tube (Last)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.107662808521704</v>
+        <v>0.8986168787996079</v>
       </c>
       <c r="D10" t="n">
-        <v>1.083013786047571</v>
+        <v>0.8525688826565255</v>
       </c>
       <c r="E10" t="n">
-        <v>1.132872834296771</v>
+        <v>0.9471519677652506</v>
       </c>
       <c r="F10" t="n">
-        <v>5.313866564512351e-19</v>
+        <v>6.802782024170647e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADL_std</t>
+          <t>性別_is_male</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ADL Standard Deviation</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.784184541613825</v>
+        <v>1.198071948246493</v>
       </c>
       <c r="D11" t="n">
-        <v>1.739106497964667</v>
+        <v>1.164760353118209</v>
       </c>
       <c r="E11" t="n">
-        <v>1.830431018605975</v>
+        <v>1.232336239237939</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3.457704667882285e-36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>first_has_feeding_tube</t>
+          <t>BW_last</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Has Feeding Tube (First)</t>
+          <t>Body Weight (Last)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.145883376320948</v>
+        <v>0.9210432158747435</v>
       </c>
       <c r="D12" t="n">
-        <v>1.094115332037099</v>
+        <v>0.8964662374146449</v>
       </c>
       <c r="E12" t="n">
-        <v>1.200100824548332</v>
+        <v>0.9462939819745976</v>
       </c>
       <c r="F12" t="n">
-        <v>7.766818790634168e-09</v>
+        <v>2.516333406957625e-09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>last_has_feeding_tube</t>
+          <t>ADL_last_CouldNot</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Has Feeding Tube (Last)</t>
+          <t>ADL Last Could Not Perform</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.8796406646364379</v>
+        <v>0.9144264741269067</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8377322226323609</v>
+        <v>0.8781959915827143</v>
       </c>
       <c r="E13" t="n">
-        <v>0.923645620853243</v>
+        <v>0.9521516661413841</v>
       </c>
       <c r="F13" t="n">
-        <v>2.617197812391748e-07</v>
+        <v>1.443589630592657e-05</v>
       </c>
     </row>
   </sheetData>
